--- a/SLR/Full-Paper-Read/Paper-Review/PS13.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS13.xlsx
@@ -26,73 +26,75 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The paper discusses experiences from a project aiming to support an ecosystem of various software platforms from villages and other rural areas. The project aims to improve the services in remote areast through an integrated software ecosystem. The authors report on experince from a project in this context.</t>
-  </si>
-  <si>
-    <t>The paper only discusses experiences and challenges, no implementation details are really provided.</t>
+    <t>The digital transformation significantly impacts the efficiency of place-based and bottom-up innovation policies across various spatial scales by altering policy-design routines in cities and regions. Digital technologies foster more open, global, participatory, and experimental innovation systems in smart places such as cities, districts, neighborhoods, and ecosystems. The integration of artificial, human, and collective intelligence is poised to transform the creation and evolution of smart places.
+Cyber-physical systems of innovation, facilitated by digital companions and collaborative efforts across physical, social, and digital spaces, enable actors to use complex, software-guided methods and derive insights from data and analytics. The paper highlights the case study of OnlineS3, a Horizon 2020 project that developed a digital platform comprising applications, datasets, and roadmaps. This platform empowers the design of smart specialization strategies for local and regional innovation systems.
+Results indicate that digital transformation enables the implementation of previously unused methodologies by policymakers due to capability constraints. It also enhances the scalability of indicators, aiding decision-making across various spatial scales and addressing the complexity of innovation systems with dynamic and diverse information.</t>
+  </si>
+  <si>
+    <t>In the paper they argue for more participatory decision-making (a form of collaboration)</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
+    <t>OnlineS3, a Horizon 2020 project</t>
+  </si>
+  <si>
+    <t>SECO Tools Availability (add repository or website in the comment)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>There are tools, guideliens and project links but not yet available (page not found)</t>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Intelligence and automation</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>Interoperability, stakeholder engagement</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ1?</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>The paper presents the OnlineS3 framework and platform, not yet available</t>
+  </si>
+  <si>
+    <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
+  </si>
+  <si>
+    <t>OnlineS3 approach, the authors uses a survey to evaluate the benefits of the proposed platform</t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ2?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I think we should note their emphasis on decision-making and participatory modelling here. Stemming from the need for increased stakeholder engagement </t>
+  </si>
+  <si>
+    <t>Application Domain(s) (at least one or domain independent)</t>
+  </si>
+  <si>
+    <t>Application Domain Independent</t>
+  </si>
+  <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>SECO Tools Availability (add repository or website in the comment)</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>Requirements engineering</t>
-  </si>
-  <si>
-    <t>Continuous software and system engineering</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>Many stakeholders, quick development need, architecture</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ1?</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
-  </si>
-  <si>
-    <t>Very loosely talking about how to perform some collaboration, but no explicity methods or examples</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ2?</t>
-  </si>
-  <si>
-    <t>In the paper they discuss how the collaboration and integration of the SECO was achieved, and various successes. Such as collaboration through listening and building trust with the target users, and having workshops to understand the needs. They benefited from a user-inteface focus in development, in addition to many types of prototypes. DevOps principles for testing.</t>
-  </si>
-  <si>
-    <t>Application Domain(s) (at least one or domain independent)</t>
-  </si>
-  <si>
-    <t>Digital Life</t>
-  </si>
-  <si>
-    <t>Smart city</t>
-  </si>
-  <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
-  </si>
-  <si>
-    <t>The paper is very short, and not structured like a typical research paper, so I think that the quality from a research perspective is quite low, althrough there are some interesting discussions</t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -568,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -601,13 +603,13 @@
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -619,28 +621,25 @@
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -690,6 +689,9 @@
     <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
     <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
@@ -698,6 +700,9 @@
     </xf>
     <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -965,7 +970,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="2.5"/>
-    <col customWidth="1" min="2" max="2" width="62.38"/>
+    <col customWidth="1" min="2" max="2" width="33.88"/>
     <col customWidth="1" min="3" max="3" width="9.0"/>
     <col customWidth="1" min="4" max="4" width="9.88"/>
     <col customWidth="1" min="5" max="5" width="9.0"/>
@@ -1012,7 +1017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="82.5" customHeight="1">
+    <row r="3" ht="250.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1058,7 +1063,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1066,16 +1071,16 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="17" t="s">
         <v>13</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>14</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>14</v>
@@ -1105,19 +1110,19 @@
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="26" t="s">
-        <v>7</v>
+      <c r="I7" s="23" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>9</v>
+      <c r="B8" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -1125,17 +1130,17 @@
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
       <c r="I8" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="67.5" customHeight="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="16">
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="25"/>
@@ -1143,8 +1148,8 @@
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="30" t="s">
-        <v>21</v>
+      <c r="I9" s="21" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1152,28 +1157,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="32" t="s">
+      <c r="C10" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="E10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="F10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="23" t="s">
-        <v>24</v>
+      <c r="H10" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1181,29 +1186,29 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="33">
+        <v>26</v>
+      </c>
+      <c r="C11" s="31">
         <f>Quality!C29</f>
-        <v>3.518518519</v>
+        <v>4.814814815</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="30" t="s">
-        <v>26</v>
+      <c r="I11" s="32" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="33" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="33" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2263,231 +2268,231 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="41">
         <v>1.0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="43"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="43"/>
+      <c r="C3" s="41">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4">
-      <c r="A4" s="44"/>
-      <c r="B4" s="41" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="44">
         <v>0.5</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
     </row>
     <row r="5">
-      <c r="A5" s="44"/>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="44">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="43"/>
+      <c r="B6" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="44">
         <v>0.5</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="44"/>
-      <c r="B6" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="45">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
     </row>
     <row r="7">
-      <c r="A7" s="46"/>
-      <c r="B7" s="41" t="s">
+      <c r="A7" s="45"/>
+      <c r="B7" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="42">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="47">
+      <c r="C7" s="44">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="46">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="46">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="49">
         <v>0.0</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
     </row>
     <row r="9">
-      <c r="A9" s="44"/>
-      <c r="B9" s="49" t="s">
+      <c r="A9" s="43"/>
+      <c r="B9" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="49">
         <v>0.0</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
     </row>
     <row r="10">
-      <c r="A10" s="44"/>
-      <c r="B10" s="49" t="s">
+      <c r="A10" s="43"/>
+      <c r="B10" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="43"/>
+      <c r="B11" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="43"/>
+      <c r="B12" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="43"/>
+      <c r="B13" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="43"/>
+      <c r="B14" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="49">
         <v>0.0</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44"/>
-      <c r="B11" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="50">
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="43"/>
+      <c r="B15" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="50">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="43"/>
+      <c r="B16" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="49">
         <v>0.0</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="50">
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="43"/>
+      <c r="B17" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="49">
         <v>0.0</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="44"/>
-      <c r="B13" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="44"/>
-      <c r="B14" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="44"/>
-      <c r="B15" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="44"/>
-      <c r="B16" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="50">
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="43"/>
+      <c r="B18" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="49">
         <v>0.0</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="44"/>
-      <c r="B18" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="50">
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45"/>
+      <c r="B19" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="49">
         <v>0.0</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="46"/>
-      <c r="B19" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="D19" s="47">
+      <c r="D19" s="46">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="46">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>2.083333333</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -2498,127 +2503,127 @@
         <v>52</v>
       </c>
       <c r="C20" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
     </row>
     <row r="21">
-      <c r="A21" s="44"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="52" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
     </row>
     <row r="22">
-      <c r="A22" s="44"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="53">
         <v>0.5</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23">
-      <c r="A23" s="44"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="52" t="s">
         <v>55</v>
       </c>
       <c r="C23" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="43"/>
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="42"/>
     </row>
     <row r="24">
-      <c r="A24" s="44"/>
+      <c r="A24" s="43"/>
       <c r="B24" s="52" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="53">
-        <v>0.0</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="43"/>
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="42"/>
     </row>
     <row r="25">
-      <c r="A25" s="46"/>
+      <c r="A25" s="45"/>
       <c r="B25" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="D25" s="54">
+      <c r="C25" s="54">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="55">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="55">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>2.5</v>
-      </c>
-      <c r="F25" s="43"/>
+        <v>5</v>
+      </c>
+      <c r="F25" s="42"/>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="58">
         <v>1.0</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="43"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="42"/>
     </row>
     <row r="27">
-      <c r="A27" s="44"/>
-      <c r="B27" s="56" t="s">
+      <c r="A27" s="43"/>
+      <c r="B27" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="58">
+      <c r="C27" s="59">
         <v>0.5</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="43"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="42"/>
     </row>
     <row r="28">
-      <c r="A28" s="46"/>
-      <c r="B28" s="56" t="s">
+      <c r="A28" s="45"/>
+      <c r="B28" s="57" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="58">
         <v>1.0</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="55">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="55">
         <f>(SUM(C26:C28)/D28)*10</f>
         <v>8.333333333</v>
       </c>
-      <c r="F28" s="43"/>
+      <c r="F28" s="42"/>
     </row>
     <row r="29">
-      <c r="B29" s="59">
+      <c r="B29" s="60">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="60">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>3.518518519</v>
+        <v>4.814814815</v>
       </c>
     </row>
   </sheetData>
